--- a/IT23677296-Assignment 1 - Test cases.xlsx
+++ b/IT23677296-Assignment 1 - Test cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e015135ffccfcbc4/Desktop/Y3 S1/ITPM/IT23677296/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS VIVOBOOK\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_5B8DE0BED50671958E1B3BB0C1F6F5C95658FB12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1BBC04DA-0B59-4598-9210-87E71827251A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532DC49C-66A7-4F19-9109-F717E965248A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="233">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -647,13 +647,85 @@
   </si>
   <si>
     <t>මචන් මම අද office ගියා නිසා ගොඩක් tired වුණා. ඒ නිසා මම හෙට work එකට එන්නේ නැද්ද කියලා හිතන් ඉන්නේ. ඔයාට පුලුවන්නම් manager ට කියන්න මම sick කියලා leave එකක් දාන්න කියලා. එහෙම නැත්නම් මම email එකක් යන්න try කරන්නම් but දැන් මට හරියට හිතෙන්නේ නෑ.</t>
+  </si>
+  <si>
+    <t>Singlish input types covered</t>
+  </si>
+  <si>
+    <t>Evidence or relational</t>
+  </si>
+  <si>
+    <t>Mixed Language</t>
+  </si>
+  <si>
+    <t>Question Form</t>
+  </si>
+  <si>
+    <t>Standard Conversational</t>
+  </si>
+  <si>
+    <t>Slang/Informal</t>
+  </si>
+  <si>
+    <t>Digital Entity (URL/Email)</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("office", "manager", "leave") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("office", "document") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>General conversational Singlish sentence to test basic phonetic mapping.</t>
+  </si>
+  <si>
+    <t>Contains an Email address to test if technical strings remain unaltered.</t>
+  </si>
+  <si>
+    <t>Contains a question mark within a URL context to test interrogative transliteration.</t>
+  </si>
+  <si>
+    <t>Uses local informal terms ("Patta", "ban") to test handling of slang.</t>
+  </si>
+  <si>
+    <t>Uses local informal terms ("Ado", "cupiri") to test handling of slang.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("report") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("Iphone") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Contains a question mark to test interrogative transliteration.</t>
+  </si>
+  <si>
+    <t>Contains a URL to test if technical strings remain unaltered.</t>
+  </si>
+  <si>
+    <t>Uses informal context to test the system's ability to handle brand-related slang.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("phone") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Uses local informal terms ("machan") to test the system's ability to handle slang.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("office") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("traffic") within a Singlish sentence to test code-switching.</t>
+  </si>
+  <si>
+    <t>Contains English nouns ("password") within a Singlish sentence to test code-switching.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,13 +757,6 @@
       <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -753,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -775,9 +840,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,10 +855,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1062,21 +1120,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G201"/>
-  <sheetFormatPr defaultRowHeight="49.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H201"/>
+  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="10" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" customWidth="1"/>
+    <col min="8" max="8" width="28.21875" customWidth="1"/>
+    <col min="9" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,9 +1153,14 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -1116,32 +1179,44 @@
       <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -1160,32 +1235,44 @@
       <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" ht="56.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
@@ -1204,32 +1291,44 @@
       <c r="F10" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-    </row>
-    <row r="14" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1248,32 +1347,44 @@
       <c r="F14" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>25</v>
       </c>
@@ -1292,32 +1403,44 @@
       <c r="F18" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>29</v>
       </c>
@@ -1336,32 +1459,44 @@
       <c r="F22" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>33</v>
       </c>
@@ -1380,32 +1515,44 @@
       <c r="F26" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G26" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-    </row>
-    <row r="30" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
@@ -1424,32 +1571,44 @@
       <c r="F30" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G30" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>41</v>
       </c>
@@ -1468,32 +1627,44 @@
       <c r="F34" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+    </row>
+    <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
-    </row>
-    <row r="37" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+    </row>
+    <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>45</v>
       </c>
@@ -1512,32 +1683,44 @@
       <c r="F38" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
-    </row>
-    <row r="40" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+    </row>
+    <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
-    </row>
-    <row r="41" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+    </row>
+    <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
-    </row>
-    <row r="42" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+    </row>
+    <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>49</v>
       </c>
@@ -1556,32 +1739,44 @@
       <c r="F42" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G42" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
-    </row>
-    <row r="44" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
-    </row>
-    <row r="45" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+    </row>
+    <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
         <v>53</v>
       </c>
@@ -1600,32 +1795,44 @@
       <c r="F46" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G46" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-    </row>
-    <row r="48" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-    </row>
-    <row r="50" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+    </row>
+    <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
         <v>57</v>
       </c>
@@ -1644,32 +1851,44 @@
       <c r="F50" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G50" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
-    </row>
-    <row r="52" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
-    </row>
-    <row r="53" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+    </row>
+    <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-    </row>
-    <row r="54" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+    </row>
+    <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
         <v>61</v>
       </c>
@@ -1688,32 +1907,44 @@
       <c r="F54" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G54" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
-    </row>
-    <row r="56" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
-    </row>
-    <row r="57" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+    </row>
+    <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-    </row>
-    <row r="58" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+    </row>
+    <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
         <v>65</v>
       </c>
@@ -1732,32 +1963,44 @@
       <c r="F58" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G58" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
-    </row>
-    <row r="60" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
-    </row>
-    <row r="61" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+    </row>
+    <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-    </row>
-    <row r="62" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+    </row>
+    <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
         <v>69</v>
       </c>
@@ -1776,32 +2019,44 @@
       <c r="F62" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
-    </row>
-    <row r="64" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+    </row>
+    <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
-    </row>
-    <row r="65" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+    </row>
+    <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
-    </row>
-    <row r="66" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+    </row>
+    <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
         <v>73</v>
       </c>
@@ -1820,32 +2075,44 @@
       <c r="F66" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G66" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
-    </row>
-    <row r="68" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+    </row>
+    <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
-    </row>
-    <row r="69" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+    </row>
+    <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-    </row>
-    <row r="70" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+    </row>
+    <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
         <v>77</v>
       </c>
@@ -1864,32 +2131,44 @@
       <c r="F70" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G70" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
-    </row>
-    <row r="72" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+    </row>
+    <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
-    </row>
-    <row r="73" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+    </row>
+    <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-    </row>
-    <row r="74" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G73" s="4"/>
+      <c r="H73" s="4"/>
+    </row>
+    <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
         <v>81</v>
       </c>
@@ -1908,32 +2187,44 @@
       <c r="F74" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G74" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+    </row>
+    <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
-    </row>
-    <row r="77" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
-    </row>
-    <row r="78" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+    </row>
+    <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
         <v>85</v>
       </c>
@@ -1952,32 +2243,44 @@
       <c r="F78" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G78" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
-    </row>
-    <row r="80" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+    </row>
+    <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
-    </row>
-    <row r="81" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+    </row>
+    <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
-    </row>
-    <row r="82" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>89</v>
       </c>
@@ -1996,32 +2299,44 @@
       <c r="F82" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G82" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
-    </row>
-    <row r="84" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+    </row>
+    <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
-    </row>
-    <row r="85" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+    </row>
+    <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
-    </row>
-    <row r="86" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+    </row>
+    <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="s">
         <v>93</v>
       </c>
@@ -2040,32 +2355,44 @@
       <c r="F86" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G86" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
-    </row>
-    <row r="88" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+    </row>
+    <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
-    </row>
-    <row r="89" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+    </row>
+    <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
-    </row>
-    <row r="90" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G89" s="4"/>
+      <c r="H89" s="4"/>
+    </row>
+    <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
         <v>97</v>
       </c>
@@ -2084,32 +2411,44 @@
       <c r="F90" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G90" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
-    </row>
-    <row r="92" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+    </row>
+    <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
-    </row>
-    <row r="93" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+    </row>
+    <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
-    </row>
-    <row r="94" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+    </row>
+    <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
         <v>101</v>
       </c>
@@ -2128,32 +2467,44 @@
       <c r="F94" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G94" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
-    </row>
-    <row r="96" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+    </row>
+    <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
-    </row>
-    <row r="97" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+    </row>
+    <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
-    </row>
-    <row r="98" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+    </row>
+    <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>105</v>
       </c>
@@ -2172,32 +2523,44 @@
       <c r="F98" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G98" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
-    </row>
-    <row r="100" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+    </row>
+    <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
-    </row>
-    <row r="101" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+    </row>
+    <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
-    </row>
-    <row r="102" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+    </row>
+    <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
         <v>109</v>
       </c>
@@ -2216,32 +2579,44 @@
       <c r="F102" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G102" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
-    </row>
-    <row r="104" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+    </row>
+    <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
-    </row>
-    <row r="105" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+    </row>
+    <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
-    </row>
-    <row r="106" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+    </row>
+    <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="5" t="s">
         <v>113</v>
       </c>
@@ -2260,32 +2635,44 @@
       <c r="F106" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G106" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
-    </row>
-    <row r="108" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+    </row>
+    <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
-    </row>
-    <row r="109" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+    </row>
+    <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
-    </row>
-    <row r="110" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+    </row>
+    <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="s">
         <v>117</v>
       </c>
@@ -2304,32 +2691,44 @@
       <c r="F110" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G110" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
-    </row>
-    <row r="112" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+    </row>
+    <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
-    </row>
-    <row r="113" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
-    </row>
-    <row r="114" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+    </row>
+    <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="s">
         <v>121</v>
       </c>
@@ -2348,32 +2747,44 @@
       <c r="F114" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G114" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
-    </row>
-    <row r="116" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+    </row>
+    <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
-    </row>
-    <row r="117" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+    </row>
+    <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
-    </row>
-    <row r="118" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+    </row>
+    <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="s">
         <v>125</v>
       </c>
@@ -2392,32 +2803,44 @@
       <c r="F118" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G118" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
-    </row>
-    <row r="120" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+    </row>
+    <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
-    </row>
-    <row r="121" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+    </row>
+    <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
-    </row>
-    <row r="122" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+    </row>
+    <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="5" t="s">
         <v>129</v>
       </c>
@@ -2436,32 +2859,44 @@
       <c r="F122" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G122" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
-    </row>
-    <row r="124" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G123" s="3"/>
+      <c r="H123" s="3"/>
+    </row>
+    <row r="124" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
-    </row>
-    <row r="125" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G124" s="3"/>
+      <c r="H124" s="3"/>
+    </row>
+    <row r="125" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
-    </row>
-    <row r="126" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+    </row>
+    <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="5" t="s">
         <v>133</v>
       </c>
@@ -2480,32 +2915,44 @@
       <c r="F126" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G126" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
-    </row>
-    <row r="128" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G127" s="3"/>
+      <c r="H127" s="3"/>
+    </row>
+    <row r="128" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
-    </row>
-    <row r="129" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G128" s="3"/>
+      <c r="H128" s="3"/>
+    </row>
+    <row r="129" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
-    </row>
-    <row r="130" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+    </row>
+    <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="5" t="s">
         <v>137</v>
       </c>
@@ -2524,32 +2971,44 @@
       <c r="F130" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G130" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
-    </row>
-    <row r="132" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G131" s="3"/>
+      <c r="H131" s="3"/>
+    </row>
+    <row r="132" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
-    </row>
-    <row r="133" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+    </row>
+    <row r="133" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
-    </row>
-    <row r="134" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+    </row>
+    <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="5" t="s">
         <v>141</v>
       </c>
@@ -2568,32 +3027,44 @@
       <c r="F134" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G134" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
-    </row>
-    <row r="136" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G135" s="3"/>
+      <c r="H135" s="3"/>
+    </row>
+    <row r="136" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
-    </row>
-    <row r="137" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+    </row>
+    <row r="137" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
-    </row>
-    <row r="138" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+    </row>
+    <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="5" t="s">
         <v>145</v>
       </c>
@@ -2612,32 +3083,44 @@
       <c r="F138" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G138" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
-    </row>
-    <row r="140" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G139" s="3"/>
+      <c r="H139" s="3"/>
+    </row>
+    <row r="140" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
-    </row>
-    <row r="141" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+    </row>
+    <row r="141" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
-    </row>
-    <row r="142" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+    </row>
+    <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>149</v>
       </c>
@@ -2656,32 +3139,44 @@
       <c r="F142" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G142" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
-    </row>
-    <row r="144" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G143" s="3"/>
+      <c r="H143" s="3"/>
+    </row>
+    <row r="144" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
-    </row>
-    <row r="145" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
-    </row>
-    <row r="146" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+    </row>
+    <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="s">
         <v>153</v>
       </c>
@@ -2700,32 +3195,44 @@
       <c r="F146" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G146" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
-    </row>
-    <row r="148" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+    </row>
+    <row r="148" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
-    </row>
-    <row r="149" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G148" s="3"/>
+      <c r="H148" s="3"/>
+    </row>
+    <row r="149" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
-    </row>
-    <row r="150" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+    </row>
+    <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="5" t="s">
         <v>157</v>
       </c>
@@ -2744,32 +3251,44 @@
       <c r="F150" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G150" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
-    </row>
-    <row r="152" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G151" s="3"/>
+      <c r="H151" s="3"/>
+    </row>
+    <row r="152" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
-    </row>
-    <row r="153" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+    </row>
+    <row r="153" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
-    </row>
-    <row r="154" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+    </row>
+    <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="5" t="s">
         <v>161</v>
       </c>
@@ -2788,32 +3307,44 @@
       <c r="F154" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G154" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
-    </row>
-    <row r="156" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G155" s="3"/>
+      <c r="H155" s="3"/>
+    </row>
+    <row r="156" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
-    </row>
-    <row r="157" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
-    </row>
-    <row r="158" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="5" t="s">
         <v>165</v>
       </c>
@@ -2832,32 +3363,44 @@
       <c r="F158" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G158" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
-    </row>
-    <row r="160" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+    </row>
+    <row r="160" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
-    </row>
-    <row r="161" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+    </row>
+    <row r="161" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
-    </row>
-    <row r="162" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="5" t="s">
         <v>169</v>
       </c>
@@ -2876,32 +3419,44 @@
       <c r="F162" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G162" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
-    </row>
-    <row r="164" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G163" s="3"/>
+      <c r="H163" s="3"/>
+    </row>
+    <row r="164" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
-    </row>
-    <row r="165" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
-    </row>
-    <row r="166" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G165" s="4"/>
+      <c r="H165" s="4"/>
+    </row>
+    <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="5" t="s">
         <v>173</v>
       </c>
@@ -2920,32 +3475,44 @@
       <c r="F166" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G166" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
-    </row>
-    <row r="168" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+    </row>
+    <row r="168" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
-    </row>
-    <row r="169" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G168" s="3"/>
+      <c r="H168" s="3"/>
+    </row>
+    <row r="169" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
-    </row>
-    <row r="170" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G169" s="4"/>
+      <c r="H169" s="4"/>
+    </row>
+    <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="5" t="s">
         <v>177</v>
       </c>
@@ -2964,32 +3531,44 @@
       <c r="F170" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G170" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
-    </row>
-    <row r="172" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G171" s="3"/>
+      <c r="H171" s="3"/>
+    </row>
+    <row r="172" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
-    </row>
-    <row r="173" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+    </row>
+    <row r="173" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
-    </row>
-    <row r="174" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G173" s="4"/>
+      <c r="H173" s="4"/>
+    </row>
+    <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="5" t="s">
         <v>181</v>
       </c>
@@ -3008,32 +3587,44 @@
       <c r="F174" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G174" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
-    </row>
-    <row r="176" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G175" s="3"/>
+      <c r="H175" s="3"/>
+    </row>
+    <row r="176" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
-    </row>
-    <row r="177" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G176" s="3"/>
+      <c r="H176" s="3"/>
+    </row>
+    <row r="177" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
-    </row>
-    <row r="178" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G177" s="4"/>
+      <c r="H177" s="4"/>
+    </row>
+    <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="5" t="s">
         <v>185</v>
       </c>
@@ -3052,32 +3643,44 @@
       <c r="F178" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G178" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
-    </row>
-    <row r="180" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+    </row>
+    <row r="180" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
-    </row>
-    <row r="181" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+    </row>
+    <row r="181" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
-    </row>
-    <row r="182" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G181" s="4"/>
+      <c r="H181" s="4"/>
+    </row>
+    <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="5" t="s">
         <v>189</v>
       </c>
@@ -3096,32 +3699,44 @@
       <c r="F182" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G182" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
-    </row>
-    <row r="184" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+    </row>
+    <row r="184" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
-    </row>
-    <row r="185" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
-    </row>
-    <row r="186" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="5" t="s">
         <v>193</v>
       </c>
@@ -3140,32 +3755,44 @@
       <c r="F186" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G186" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
-    </row>
-    <row r="188" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+    </row>
+    <row r="188" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
-    </row>
-    <row r="189" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+    </row>
+    <row r="189" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
-    </row>
-    <row r="190" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
+    </row>
+    <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="5" t="s">
         <v>197</v>
       </c>
@@ -3184,32 +3811,44 @@
       <c r="F190" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G190" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
-    </row>
-    <row r="192" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+    </row>
+    <row r="192" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
-    </row>
-    <row r="193" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+    </row>
+    <row r="193" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
-    </row>
-    <row r="194" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G193" s="4"/>
+      <c r="H193" s="4"/>
+    </row>
+    <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="5" t="s">
         <v>201</v>
       </c>
@@ -3228,32 +3867,44 @@
       <c r="F194" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G194" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
-    </row>
-    <row r="196" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G195" s="3"/>
+      <c r="H195" s="3"/>
+    </row>
+    <row r="196" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
-    </row>
-    <row r="197" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G196" s="3"/>
+      <c r="H196" s="3"/>
+    </row>
+    <row r="197" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
-    </row>
-    <row r="198" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G197" s="4"/>
+      <c r="H197" s="4"/>
+    </row>
+    <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="5" t="s">
         <v>205</v>
       </c>
@@ -3272,33 +3923,45 @@
       <c r="F198" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G198" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
-    </row>
-    <row r="200" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G199" s="3"/>
+      <c r="H199" s="3"/>
+    </row>
+    <row r="200" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
-    </row>
-    <row r="201" spans="1:6" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G200" s="3"/>
+      <c r="H200" s="3"/>
+    </row>
+    <row r="201" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
+      <c r="G201" s="4"/>
+      <c r="H201" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="300">
+  <mergeCells count="400">
     <mergeCell ref="C14:C17"/>
     <mergeCell ref="C98:C101"/>
     <mergeCell ref="C154:C157"/>
@@ -3313,8 +3976,16 @@
     <mergeCell ref="A118:A121"/>
     <mergeCell ref="E86:E89"/>
     <mergeCell ref="B34:B37"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="C162:C165"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="C118:C121"/>
     <mergeCell ref="F42:F45"/>
     <mergeCell ref="B78:B81"/>
     <mergeCell ref="D78:D81"/>
@@ -3323,18 +3994,10 @@
     <mergeCell ref="C86:C89"/>
     <mergeCell ref="F82:F85"/>
     <mergeCell ref="D54:D57"/>
-    <mergeCell ref="C162:C165"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A54:A57"/>
     <mergeCell ref="D46:D49"/>
     <mergeCell ref="C54:C57"/>
-    <mergeCell ref="A74:A77"/>
     <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="E62:E65"/>
     <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
@@ -3431,30 +4094,6 @@
     <mergeCell ref="C70:C73"/>
     <mergeCell ref="F102:F105"/>
     <mergeCell ref="E70:E73"/>
-    <mergeCell ref="F190:F193"/>
-    <mergeCell ref="B30:B33"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="C178:C181"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="E178:E181"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="C166:C169"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="E190:E193"/>
-    <mergeCell ref="D158:D161"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="D154:D157"/>
-    <mergeCell ref="B178:B181"/>
     <mergeCell ref="B198:B201"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="A106:A109"/>
@@ -3479,9 +4118,6 @@
     <mergeCell ref="C126:C129"/>
     <mergeCell ref="F162:F165"/>
     <mergeCell ref="B94:B97"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="A158:A161"/>
-    <mergeCell ref="D186:D189"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A50:A53"/>
     <mergeCell ref="C50:C53"/>
@@ -3496,21 +4132,16 @@
     <mergeCell ref="D66:D69"/>
     <mergeCell ref="D106:D109"/>
     <mergeCell ref="F66:F69"/>
-    <mergeCell ref="B146:B149"/>
     <mergeCell ref="D18:D21"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="F30:F33"/>
     <mergeCell ref="E38:E41"/>
-    <mergeCell ref="F158:F161"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="D118:D121"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="D130:D133"/>
     <mergeCell ref="F130:F133"/>
@@ -3528,9 +4159,37 @@
     <mergeCell ref="F26:F29"/>
     <mergeCell ref="F154:F157"/>
     <mergeCell ref="F134:F137"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="A158:A161"/>
+    <mergeCell ref="B146:B149"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="F158:F161"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="E194:E197"/>
+    <mergeCell ref="B150:B153"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="C170:C173"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="C174:C177"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="B190:B193"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D186:D189"/>
+    <mergeCell ref="E166:E169"/>
+    <mergeCell ref="F190:F193"/>
+    <mergeCell ref="C178:C181"/>
+    <mergeCell ref="E178:E181"/>
+    <mergeCell ref="C166:C169"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="E190:E193"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
     <mergeCell ref="F58:F61"/>
@@ -3543,17 +4202,18 @@
     <mergeCell ref="C186:C189"/>
     <mergeCell ref="D94:D97"/>
     <mergeCell ref="E142:E145"/>
-    <mergeCell ref="E194:E197"/>
-    <mergeCell ref="B150:B153"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="C170:C173"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="C174:C177"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="D158:D161"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="D154:D157"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="E74:E77"/>
     <mergeCell ref="D6:D9"/>
     <mergeCell ref="C26:C29"/>
     <mergeCell ref="D190:D193"/>
@@ -3577,6 +4237,7 @@
     <mergeCell ref="D134:D137"/>
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
+    <mergeCell ref="E22:E25"/>
     <mergeCell ref="A98:A101"/>
     <mergeCell ref="A198:A201"/>
     <mergeCell ref="F194:F197"/>
@@ -3599,6 +4260,108 @@
     <mergeCell ref="B114:B117"/>
     <mergeCell ref="D114:D117"/>
     <mergeCell ref="B154:B157"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="G6:G9"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="G30:G33"/>
+    <mergeCell ref="G34:G37"/>
+    <mergeCell ref="G98:G101"/>
+    <mergeCell ref="G102:G105"/>
+    <mergeCell ref="G106:G109"/>
+    <mergeCell ref="G38:G41"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="G46:G49"/>
+    <mergeCell ref="G50:G53"/>
+    <mergeCell ref="G54:G57"/>
+    <mergeCell ref="G58:G61"/>
+    <mergeCell ref="G62:G65"/>
+    <mergeCell ref="G66:G69"/>
+    <mergeCell ref="G70:G73"/>
+    <mergeCell ref="H74:H77"/>
+    <mergeCell ref="H78:H81"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="G146:G149"/>
+    <mergeCell ref="G150:G153"/>
+    <mergeCell ref="G154:G157"/>
+    <mergeCell ref="G158:G161"/>
+    <mergeCell ref="G162:G165"/>
+    <mergeCell ref="G166:G169"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="G118:G121"/>
+    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="G126:G129"/>
+    <mergeCell ref="G130:G133"/>
+    <mergeCell ref="G134:G137"/>
+    <mergeCell ref="G138:G141"/>
+    <mergeCell ref="G142:G145"/>
+    <mergeCell ref="G74:G77"/>
+    <mergeCell ref="G78:G81"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="G94:G97"/>
+    <mergeCell ref="H38:H41"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="H46:H49"/>
+    <mergeCell ref="H50:H53"/>
+    <mergeCell ref="H54:H57"/>
+    <mergeCell ref="H58:H61"/>
+    <mergeCell ref="H62:H65"/>
+    <mergeCell ref="H66:H69"/>
+    <mergeCell ref="H70:H73"/>
+    <mergeCell ref="H2:H5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="H10:H13"/>
+    <mergeCell ref="H14:H17"/>
+    <mergeCell ref="H18:H21"/>
+    <mergeCell ref="H22:H25"/>
+    <mergeCell ref="H26:H29"/>
+    <mergeCell ref="H30:H33"/>
+    <mergeCell ref="H34:H37"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="H130:H133"/>
+    <mergeCell ref="H134:H137"/>
+    <mergeCell ref="H138:H141"/>
+    <mergeCell ref="H142:H145"/>
+    <mergeCell ref="H146:H149"/>
+    <mergeCell ref="H150:H153"/>
+    <mergeCell ref="H154:H157"/>
+    <mergeCell ref="H194:H197"/>
+    <mergeCell ref="H198:H201"/>
+    <mergeCell ref="G194:G197"/>
+    <mergeCell ref="G198:G201"/>
+    <mergeCell ref="H158:H161"/>
+    <mergeCell ref="H162:H165"/>
+    <mergeCell ref="H166:H169"/>
+    <mergeCell ref="H170:H173"/>
+    <mergeCell ref="H174:H177"/>
+    <mergeCell ref="H178:H181"/>
+    <mergeCell ref="H182:H185"/>
+    <mergeCell ref="H186:H189"/>
+    <mergeCell ref="H190:H193"/>
+    <mergeCell ref="G182:G185"/>
+    <mergeCell ref="G186:G189"/>
+    <mergeCell ref="G190:G193"/>
+    <mergeCell ref="G170:G173"/>
+    <mergeCell ref="G174:G177"/>
+    <mergeCell ref="G178:G181"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
